--- a/Philly_Ratings.xlsx
+++ b/Philly_Ratings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Philly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,6 +527,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Google Maps Name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded Sources</t>
         </is>
       </c>
     </row>
@@ -549,7 +555,7 @@
         <v>4.119</v>
       </c>
       <c r="L2" t="n">
-        <v>17.4</v>
+        <v>18.2</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -557,6 +563,7 @@
           <t>Little Walter’s</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,7 +585,7 @@
         <v>4.272</v>
       </c>
       <c r="L3" t="n">
-        <v>69.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -586,6 +593,7 @@
           <t>Osteria</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -607,7 +615,7 @@
         <v>4.288</v>
       </c>
       <c r="L4" t="n">
-        <v>73.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -615,6 +623,7 @@
           <t>Post Haste</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -636,7 +645,7 @@
         <v>4.235</v>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>54.5</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -644,6 +653,7 @@
           <t>Solar Myth</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,7 +675,7 @@
         <v>4.301</v>
       </c>
       <c r="L6" t="n">
-        <v>78.3</v>
+        <v>81.8</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -673,6 +683,7 @@
           <t>Double Knot</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -690,16 +701,15 @@
       <c r="J7" t="n">
         <v>626</v>
       </c>
-      <c r="K7" t="n">
-        <v>4.346</v>
-      </c>
-      <c r="L7" t="n">
-        <v>91.3</v>
-      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bob and Barbara's Lounge</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Google rating 4.6 excluded — Google returned "Bob and Barbara's Lounge", whose name similarity to "Bob &amp; Barbara's" is 0.71 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -731,6 +741,7 @@
           <t>Talula's Garden</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -752,7 +763,7 @@
         <v>4.325</v>
       </c>
       <c r="L9" t="n">
-        <v>82.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -760,6 +771,7 @@
           <t>Loco Pez</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -781,7 +793,7 @@
         <v>4.159</v>
       </c>
       <c r="L10" t="n">
-        <v>26.1</v>
+        <v>27.3</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -789,6 +801,7 @@
           <t>Frankford Hall</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -810,7 +823,7 @@
         <v>4.231</v>
       </c>
       <c r="L11" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -818,6 +831,7 @@
           <t>SouthGate</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -839,7 +853,7 @@
         <v>4.243</v>
       </c>
       <c r="L12" t="n">
-        <v>56.5</v>
+        <v>59.1</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -847,6 +861,7 @@
           <t>The Trestle Inn</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -868,7 +883,7 @@
         <v>4.266</v>
       </c>
       <c r="L13" t="n">
-        <v>65.2</v>
+        <v>68.2</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -876,6 +891,7 @@
           <t>Urban Village Brewing Company</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -897,7 +913,7 @@
         <v>4.204</v>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>40.9</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -905,6 +921,7 @@
           <t>Sampan</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -926,7 +943,7 @@
         <v>4.069</v>
       </c>
       <c r="L15" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -934,6 +951,7 @@
           <t>Franky Bradley's | B.West</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -955,7 +973,7 @@
         <v>4.171</v>
       </c>
       <c r="L16" t="n">
-        <v>30.4</v>
+        <v>31.8</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -963,6 +981,7 @@
           <t>Strangelove's</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -981,15 +1000,20 @@
         <v>149</v>
       </c>
       <c r="K17" t="n">
-        <v>3.775</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>The Lesieur</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Google rating 4.4 excluded — Google returned 'The Lesieur', whose name similarity to 'Bar Lesieur' is 0.70 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1037,7 @@
         <v>4.247</v>
       </c>
       <c r="L18" t="n">
-        <v>60.9</v>
+        <v>63.6</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1021,6 +1045,7 @@
           <t>Lloyd</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1042,7 +1067,7 @@
         <v>4.154</v>
       </c>
       <c r="L19" t="n">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1050,6 +1075,7 @@
           <t>Harp &amp; Crown</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1071,7 +1097,7 @@
         <v>4.224</v>
       </c>
       <c r="L20" t="n">
-        <v>43.5</v>
+        <v>45.5</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1079,6 +1105,7 @@
           <t>McGillin's Olde Ale House</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1100,7 +1127,7 @@
         <v>4.344</v>
       </c>
       <c r="L21" t="n">
-        <v>87</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1108,6 +1135,7 @@
           <t>Yanaga Kappo Izakaya</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1129,7 +1157,7 @@
         <v>4.103</v>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1137,6 +1165,7 @@
           <t>Bar-Ly Chinatown</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1158,7 +1187,7 @@
         <v>4.409</v>
       </c>
       <c r="L23" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1166,6 +1195,7 @@
           <t>Tattooed Mom</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1187,7 +1217,7 @@
         <v>4.193</v>
       </c>
       <c r="L24" t="n">
-        <v>34.8</v>
+        <v>36.4</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1195,6 +1225,7 @@
           <t>Mission Taqueria</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1216,7 +1247,7 @@
         <v>3.666</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -1224,6 +1255,7 @@
           <t>Bleu Martini</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
